--- a/artfynd/A 6514-2025 artfynd.xlsx
+++ b/artfynd/A 6514-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123727099</v>
+        <v>123727250</v>
       </c>
       <c r="B2" t="n">
-        <v>79370</v>
+        <v>79902</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>662634</v>
+        <v>662687</v>
       </c>
       <c r="R2" t="n">
-        <v>7221858</v>
+        <v>7221679</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +762,6 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -778,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123727121</v>
+        <v>123727155</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>97367</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -818,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>662687</v>
+        <v>662527</v>
       </c>
       <c r="R3" t="n">
-        <v>7221679</v>
+        <v>7221893</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,6 +863,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Oskar Wallströmer</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -880,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123727155</v>
+        <v>123727236</v>
       </c>
       <c r="B4" t="n">
-        <v>97350</v>
+        <v>82573</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -892,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>662527</v>
+        <v>662621</v>
       </c>
       <c r="R4" t="n">
-        <v>7221893</v>
+        <v>7221870</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,11 +970,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Oskar Wallströmer</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -987,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123727236</v>
+        <v>123727099</v>
       </c>
       <c r="B5" t="n">
-        <v>82568</v>
+        <v>79375</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1027,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>662621</v>
+        <v>662634</v>
       </c>
       <c r="R5" t="n">
-        <v>7221870</v>
+        <v>7221858</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,6 +1073,7 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AR5" t="inlineStr"/>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
@@ -1089,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123727097</v>
+        <v>123727224</v>
       </c>
       <c r="B6" t="n">
-        <v>96264</v>
+        <v>78786</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,21 +1105,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1841</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>662838</v>
+        <v>662625</v>
       </c>
       <c r="R6" t="n">
-        <v>7221875</v>
+        <v>7221873</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>Nils Ericson</t>
+          <t>Oskar Wallströmer</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1196,10 +1196,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123727250</v>
+        <v>123727097</v>
       </c>
       <c r="B7" t="n">
-        <v>79897</v>
+        <v>96273</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1208,25 +1208,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>1841</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1236,10 +1236,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>662687</v>
+        <v>662838</v>
       </c>
       <c r="R7" t="n">
-        <v>7221679</v>
+        <v>7221875</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1282,6 +1282,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Nils Ericson</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1298,10 +1303,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123727224</v>
+        <v>123727173</v>
       </c>
       <c r="B8" t="n">
-        <v>78781</v>
+        <v>79867</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,21 +1319,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1338,10 +1343,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>662625</v>
+        <v>662684</v>
       </c>
       <c r="R8" t="n">
-        <v>7221873</v>
+        <v>7221680</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1384,11 +1389,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>Oskar Wallströmer</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1405,10 +1405,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123727173</v>
+        <v>123727121</v>
       </c>
       <c r="B9" t="n">
-        <v>79862</v>
+        <v>79896</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1417,25 +1417,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>662684</v>
+        <v>662687</v>
       </c>
       <c r="R9" t="n">
-        <v>7221680</v>
+        <v>7221679</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 6514-2025 artfynd.xlsx
+++ b/artfynd/A 6514-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123727250</v>
+        <v>123727236</v>
       </c>
       <c r="B2" t="n">
-        <v>79902</v>
+        <v>82575</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>662687</v>
+        <v>662621</v>
       </c>
       <c r="R2" t="n">
-        <v>7221679</v>
+        <v>7221870</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123727155</v>
+        <v>123727097</v>
       </c>
       <c r="B3" t="n">
-        <v>97367</v>
+        <v>96275</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>1841</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>662527</v>
+        <v>662838</v>
       </c>
       <c r="R3" t="n">
-        <v>7221893</v>
+        <v>7221875</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>Oskar Wallströmer</t>
+          <t>Nils Ericson</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123727236</v>
+        <v>123727224</v>
       </c>
       <c r="B4" t="n">
-        <v>82573</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>662621</v>
+        <v>662625</v>
       </c>
       <c r="R4" t="n">
-        <v>7221870</v>
+        <v>7221873</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,6 +970,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Oskar Wallströmer</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -989,7 +994,7 @@
         <v>123727099</v>
       </c>
       <c r="B5" t="n">
-        <v>79375</v>
+        <v>79377</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1089,10 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123727224</v>
+        <v>123727155</v>
       </c>
       <c r="B6" t="n">
-        <v>78786</v>
+        <v>97369</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1101,25 +1106,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1129,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>662625</v>
+        <v>662527</v>
       </c>
       <c r="R6" t="n">
-        <v>7221873</v>
+        <v>7221893</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,10 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123727097</v>
+        <v>123727121</v>
       </c>
       <c r="B7" t="n">
-        <v>96273</v>
+        <v>79898</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1208,25 +1213,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1841</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1236,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>662838</v>
+        <v>662687</v>
       </c>
       <c r="R7" t="n">
-        <v>7221875</v>
+        <v>7221679</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1282,11 +1287,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>Nils Ericson</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1303,10 +1303,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123727173</v>
+        <v>123727250</v>
       </c>
       <c r="B8" t="n">
-        <v>79867</v>
+        <v>79904</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1315,25 +1315,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>662684</v>
+        <v>662687</v>
       </c>
       <c r="R8" t="n">
-        <v>7221680</v>
+        <v>7221679</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,10 +1405,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123727121</v>
+        <v>123727173</v>
       </c>
       <c r="B9" t="n">
-        <v>79896</v>
+        <v>79869</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1417,25 +1417,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>662687</v>
+        <v>662684</v>
       </c>
       <c r="R9" t="n">
-        <v>7221679</v>
+        <v>7221680</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
